--- a/files/Model_Skenario_Capex.xlsx
+++ b/files/Model_Skenario_Capex.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L by BU" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,25 +26,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00707070"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="001F2D55"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00707070"/>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,10 +63,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,20 +81,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7E2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,14 +488,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -464,112 +512,1678 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Filename: Model_Skenario_Capex.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Source file: Model_Skenario_Capex.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2023A</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2024A</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>FY2026 Plan</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>FY2027F</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>FY2028F</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>FY2029F</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>FY2030F</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>-- Banking --</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Revenue (MYR M)</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1820</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2150</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2480</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Placeholder figures</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EBITDA (MYR M)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>312</v>
-      </c>
-      <c r="C6" t="n">
-        <v>378</v>
-      </c>
-      <c r="D6" t="n">
-        <v>435</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Placeholder figures</t>
-        </is>
+      <c r="B6" s="6" t="n">
+        <v>12434.2</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>12525.1</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>12763.7</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>13370.3</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>13150.1</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>13824.2</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>13941.6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Net Margin (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Placeholder figures</t>
-        </is>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>-8229.799999999999</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>-8195.4</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>-8153.1</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>-8629.1</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>-8290.4</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>-9031.200000000001</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>-9235.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>4204.4</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>4329.7</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4610.6</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>4741.2</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4859.6</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>4793</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>4706.2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder file used by the Zava Conglomerate Copilot Demo Hub. Replace with the actual workbook before live use.</t>
-        </is>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>2350.3</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>2168.4</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>2184</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>2397.1</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>2390.9</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>2383.8</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>2463.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>-- Insurance --</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3918.2</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3946</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>3958.4</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4064.6</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>4137.7</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4351</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4380.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>-2572.3</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>-2503.7</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>-2539.6</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>-2577.2</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>-2759.4</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>-2852.3</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>-2849.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1345.9</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1442.3</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1418.8</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1487.3</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1378.3</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1498.7</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1530.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>563</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>521.8</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>568.1</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>579.8</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>612.2</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>634.4</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>643.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>-- Healthcare Services --</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>5439.6</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>5477.6</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>5608.7</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>5571.2</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5707.1</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>5856.2</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>6080.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>-3566.8</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>-3574.1</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>-3580.5</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>-3690.4</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>-3641.2</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>-3813.5</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>-3883.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1872.8</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>1903.5</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>2028.3</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1880.8</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2065.9</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>2042.7</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>2196.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>845.8</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>882.2</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>913</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>843.4</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>866.3</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>981.2</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>981.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>-- Industrial Manufacturing --</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>5788.5</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>6106.6</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>6195.7</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>6226.9</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>6472.6</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>6571.6</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>6694.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>-3747.4</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>-3955.8</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>-4032.6</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>-3982.2</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>-4198.2</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>-4384.5</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>-4441.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>2041</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2150.8</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>2163.1</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>2244.6</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>2274.4</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>2187.1</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>2252.3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>777.1</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>736.2</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>774</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>786.6</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>791.4</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>828.3</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>841.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>-- Property Development --</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>4704.5</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>4810.6</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>4976.3</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>5084.8</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>5012.8</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>5181.1</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>5292</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>-3151.3</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>-3058.7</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>-3294.1</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-3231.5</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>-3210.9</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>-3316.8</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>-3361.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>1553.2</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1751.9</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1682.2</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>1853.2</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1801.9</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>1864.3</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>1930.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>1081.9</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>1082.3</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>1109.6</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>1115</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>1143.1</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>1128.7</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>1159.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>-- Oil &amp; Gas (downstream) --</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>4403.5</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>4432.2</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>4590.2</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>4658.5</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>4647.8</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>4786.5</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>4860.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>-2852.7</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>-2843</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>-2936.6</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-3029.6</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>-3035.1</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>-3079.2</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>-3255.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>1550.8</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1589.3</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>1653.6</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>1628.9</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>1612.6</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>1707.3</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>1604.8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>460.3</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>484.8</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>483</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>468.4</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>498.8</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>-- Retail Distribution --</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>2153.5</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>2130.7</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>2219.9</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>2215.6</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>2263</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>2336.1</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>2361.6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>-1405.8</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>-1356.6</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>-1439.2</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>-1440</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>-1473.8</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>-1510.1</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>-1507.3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>747.7</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>774.1</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>780.8</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>775.5</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>789.3</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>826</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>854.4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>141.2</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>169.6</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>176.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>-- Hospitality --</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>1271.4</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>1293.5</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>1333.2</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>1389.3</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>1415.9</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>1402.2</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>1460.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>-842.9</v>
+      </c>
+      <c r="C49" s="8" t="n">
+        <v>-822.4</v>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>-854.4</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-911.1</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>-946.1</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>-888.1</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>-935.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>428.5</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>471.1</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>478.8</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>478.2</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>469.8</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>514.1</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>213.3</v>
+      </c>
+      <c r="C51" s="8" t="n">
+        <v>209.1</v>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>233.1</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>225.9</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>220.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>-- Digital Infrastructure --</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>1635.4</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>1678.5</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>1733.2</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>1775.4</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>1791.4</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>1823.6</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>1898.8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>-1075.4</v>
+      </c>
+      <c r="C55" s="8" t="n">
+        <v>-1076.8</v>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>-1128.9</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-1130.9</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>-1167.9</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>-1174.7</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>-1214.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>559.9</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>601.7</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>604.3</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>644.5</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>623.4</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>649</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>684.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>560.3</v>
+      </c>
+      <c r="C57" s="8" t="n">
+        <v>577.2</v>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>598.3</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>597.5</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>603.9</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>604.8</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>643.2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>-- Education Services --</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>821.2</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>863.7</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>851.8</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>885.6</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>894.5</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>928.1</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>928.4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>-544.8</v>
+      </c>
+      <c r="C61" s="8" t="n">
+        <v>-548.1</v>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>-555.9</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>-589.2</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>-595.5</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>-613</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>-588.9</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>276.4</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>315.6</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>295.9</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>299</v>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>315</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>339.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>104.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>-- Plantation --</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Revenue (MYR M)</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>1736.3</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>1821.9</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>1864.1</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>1933.9</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>1900.2</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>1942.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>-1142.5</v>
+      </c>
+      <c r="C67" s="8" t="n">
+        <v>-1148.8</v>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>-1177.7</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>-1191.1</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>-1260.8</v>
+      </c>
+      <c r="G67" s="8" t="n">
+        <v>-1225</v>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>-1228.7</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>593.8</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>609.1</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>644.3</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>673</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>673.1</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>675.2</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>713.9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>317.4</v>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>339.4</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>365</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="G69" s="8" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>369.8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
